--- a/reports/pdf_rolling5_20260709.xlsx
+++ b/reports/pdf_rolling5_20260709.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,034억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 10종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,389억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 10종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>145</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1612165100</v>
+        <v>1639387400</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1175265000</v>
+        <v>-1195110000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2668411200</v>
+        <v>2713468800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-54</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-811076760</v>
+        <v>-824772240</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1878558500</v>
+        <v>1910279000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-52</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1457861600</v>
+        <v>-1482478400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2278255200</v>
+        <v>2316724800</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-49</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2622146800</v>
+        <v>-2666423200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1286022400</v>
+        <v>1307737600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-37</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1250311400</v>
+        <v>-1271423600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>490733100</v>
+        <v>499019400</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-25</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-3616405000</v>
+        <v>-3677470000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>447720000</v>
+        <v>455280000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-23</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2517998600</v>
+        <v>-2560516400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>3007719000</v>
+        <v>3058506000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-22</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-439255960</v>
+        <v>-446673040</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1025065600</v>
+        <v>1042374400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-929552000</v>
+        <v>-1972880000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.20%→2.09%</t>
+          <t>1.22%→0.90%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>219→199</t>
+          <t>61→41</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2440074000</v>
+        <v>2481276000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1940120000</v>
+        <v>-945248000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.90%</t>
+          <t>2.20%→2.09%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>61→41</t>
+          <t>219→199</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
         <v>-19</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1322586200</v>
+        <v>-1344918800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>-17</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-895226800</v>
+        <v>-910343200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>-16</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2582278400</v>
+        <v>-2625881600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1838956600</v>
+        <v>-1870008400</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>-13</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1144670800</v>
+        <v>-1163999200</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-436846800</v>
+        <v>-444223200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>-10</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-420537000</v>
+        <v>-427638000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-898424800</v>
+        <v>-913595200</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1332,23 +1332,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>이오테크닉스  (편출)</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-930618000</v>
+        <v>-2829240000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.26%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>6→0</t>
         </is>
       </c>
     </row>
@@ -1360,23 +1360,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-2782260000</v>
+        <v>-946332000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.47%→0.00%</t>
+          <t>1.42%→1.26%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>6→0</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         <v>-4</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-978588000</v>
+        <v>-995112000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,657억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,354억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1435,7 +1435,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,176억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>201</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>6303360000</v>
+        <v>6448080000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>-86</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-6924444800</v>
+        <v>-7083424400</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>139</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>8249483200</v>
+        <v>8438884600</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>-81</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-4788201600</v>
+        <v>-4898134800</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>8972880000</v>
+        <v>9178890000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>-66</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-7021660800</v>
+        <v>-7182872400</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>1604691200</v>
+        <v>1641533600</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>-58</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1552868800</v>
+        <v>-1588521400</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>-40</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-4562880000</v>
+        <v>-4667640000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,760억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,581억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1752,7 +1752,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 16종목  /  매도 16종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 324억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 16종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1848,11 +1848,11 @@
         <v>121</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>90764520</v>
+        <v>84361200</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>6.62%→6.88%</t>
+          <t>6.60%→6.87%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1869,11 +1869,11 @@
         <v>-318</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-105245280</v>
+        <v>-100837800</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.95%→2.64%</t>
+          <t>3.04%→2.72%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1892,11 +1892,11 @@
         <v>91</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>23390640</v>
+        <v>21479640</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.38%→0.45%</t>
+          <t>0.38%→0.44%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1913,11 +1913,11 @@
         <v>-268</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-147228480</v>
+        <v>-144752160</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.30%</t>
+          <t>0.77%→0.31%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>37</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>102408600</v>
+        <v>96658800</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -1957,11 +1957,11 @@
         <v>-87</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-257972400</v>
+        <v>-247010400</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>6.55%→5.79%</t>
+          <t>6.73%→5.95%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -1980,11 +1980,11 @@
         <v>23</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>280140000</v>
+        <v>262172400</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.31%→3.13%</t>
+          <t>2.32%→3.14%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2001,11 +2001,11 @@
         <v>-63</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-97584480</v>
+        <v>-94144680</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.20%</t>
+          <t>0.50%→0.21%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2024,11 +2024,11 @@
         <v>22</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>208269600</v>
+        <v>189789600</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.08%→2.68%</t>
+          <t>2.03%→2.62%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2045,7 +2045,7 @@
         <v>-36</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-33596640</v>
+        <v>-31540320</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2068,11 +2068,11 @@
         <v>18</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>131846400</v>
+        <v>128520000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>3.21%→3.59%</t>
+          <t>3.36%→3.76%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2089,11 +2089,11 @@
         <v>-34</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-31073280</v>
+        <v>-29816640</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.13%</t>
+          <t>0.23%→0.13%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2112,11 +2112,11 @@
         <v>12</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>52113600</v>
+        <v>48484800</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.55%→0.70%</t>
+          <t>0.54%→0.70%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2133,11 +2133,11 @@
         <v>-17</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-65331000</v>
+        <v>-62260800</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>7.26%→7.06%</t>
+          <t>7.42%→7.22%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2156,11 +2156,11 @@
         <v>11</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>17925600</v>
+        <v>17269560</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.42%</t>
+          <t>0.38%→0.43%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2177,11 +2177,11 @@
         <v>-16</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-51744000</v>
+        <v>-48384000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.65%</t>
+          <t>0.81%→0.65%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2193,88 +2193,88 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>60900000</v>
+        <v>32130000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.53%→2.70%</t>
+          <t>1.15%→1.25%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-40983600</v>
+        <v>-35103600</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.59%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>34860000</v>
+        <v>55776000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.26%</t>
+          <t>2.48%→2.66%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-36456000</v>
+        <v>-38572800</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.72%→0.60%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2288,11 +2288,11 @@
         <v>9</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>113475600</v>
+        <v>103874400</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.44%→1.77%</t>
+          <t>1.41%→1.74%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2309,11 +2309,11 @@
         <v>-13</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-112694400</v>
+        <v>-99372000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.15%</t>
+          <t>2.35%→2.04%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2332,11 +2332,11 @@
         <v>8</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>108729600</v>
+        <v>101740800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.70%</t>
+          <t>2.39%→2.71%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2353,11 +2353,11 @@
         <v>-10</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-71652000</v>
+        <v>-69048000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.79%</t>
+          <t>1.04%→0.82%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2376,11 +2376,11 @@
         <v>6</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>41076000</v>
+        <v>37396800</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.46%→1.58%</t>
+          <t>1.43%→1.54%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2397,11 +2397,11 @@
         <v>-9</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-62294400</v>
+        <v>-53600400</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.65%</t>
+          <t>2.62%→2.45%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2413,23 +2413,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>38656800</v>
+        <v>73332000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>0.87%→0.98%</t>
+          <t>1.38%→1.61%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2441,11 +2441,11 @@
         <v>-8</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-182112000</v>
+        <v>-181776000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.13%→1.60%</t>
+          <t>2.28%→1.71%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2457,23 +2457,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>70560000</v>
+        <v>34725600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.44%</t>
+          <t>0.84%→0.94%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2485,11 +2485,11 @@
         <v>-7</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-75028800</v>
+        <v>-68325600</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>3.35%→3.13%</t>
+          <t>3.28%→3.06%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2508,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>58086000</v>
+        <v>54180000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2529,11 +2529,11 @@
         <v>-6</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-23360400</v>
+        <v>-20160000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.39%→2.32%</t>
+          <t>2.21%→2.15%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 571억      오늘 2026-07-09  vs  5일전 2026-07-02      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260709.xlsx
+++ b/reports/pdf_rolling5_20260709.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1972880000</v>
+        <v>-945248000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.90%</t>
+          <t>2.20%→2.09%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>61→41</t>
+          <t>219→199</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-945248000</v>
+        <v>-1972880000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2.20%→2.09%</t>
+          <t>1.22%→0.90%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>219→199</t>
+          <t>61→41</t>
         </is>
       </c>
     </row>
@@ -2193,88 +2193,88 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>32130000</v>
+        <v>55776000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.25%</t>
+          <t>2.48%→2.66%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-35103600</v>
+        <v>-38572800</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.72%→0.60%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>55776000</v>
+        <v>32130000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.66%</t>
+          <t>1.15%→1.25%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-38572800</v>
+        <v>-35103600</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2369,23 +2369,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>37396800</v>
+        <v>34725600</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.54%</t>
+          <t>0.84%→0.94%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2457,23 +2457,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>34725600</v>
+        <v>37396800</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.84%→0.94%</t>
+          <t>1.43%→1.54%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260709.xlsx
+++ b/reports/pdf_rolling5_20260709.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-945248000</v>
+        <v>-1972880000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.20%→2.09%</t>
+          <t>1.22%→0.90%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>219→199</t>
+          <t>61→41</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1972880000</v>
+        <v>-945248000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.90%</t>
+          <t>2.20%→2.09%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>61→41</t>
+          <t>219→199</t>
         </is>
       </c>
     </row>
@@ -1332,23 +1332,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2829240000</v>
+        <v>-946332000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.47%→0.00%</t>
+          <t>1.42%→1.26%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>6→0</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -1360,23 +1360,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>이오테크닉스  (편출)</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-946332000</v>
+        <v>-2829240000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.26%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>6→0</t>
         </is>
       </c>
     </row>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-38572800</v>
+        <v>-35103600</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-35103600</v>
+        <v>-38572800</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.72%→0.60%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2413,23 +2413,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>73332000</v>
+        <v>37396800</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.38%→1.61%</t>
+          <t>1.43%→1.54%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2457,23 +2457,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>37396800</v>
+        <v>73332000</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.54%</t>
+          <t>1.38%→1.61%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260709.xlsx
+++ b/reports/pdf_rolling5_20260709.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1972880000</v>
+        <v>-945248000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.90%</t>
+          <t>2.20%→2.09%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>61→41</t>
+          <t>219→199</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-945248000</v>
+        <v>-1972880000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2.20%→2.09%</t>
+          <t>1.22%→0.90%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>219→199</t>
+          <t>61→41</t>
         </is>
       </c>
     </row>
@@ -1332,23 +1332,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>이오테크닉스  (편출)</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-946332000</v>
+        <v>-2829240000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.26%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>6→0</t>
         </is>
       </c>
     </row>
@@ -1360,23 +1360,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-2829240000</v>
+        <v>-946332000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.47%→0.00%</t>
+          <t>1.42%→1.26%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>6→0</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-35103600</v>
+        <v>-38572800</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.72%→0.60%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-38572800</v>
+        <v>-35103600</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2369,23 +2369,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>34725600</v>
+        <v>73332000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>0.84%→0.94%</t>
+          <t>1.38%→1.61%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2413,23 +2413,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>37396800</v>
+        <v>34725600</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.54%</t>
+          <t>0.84%→0.94%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2457,23 +2457,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>73332000</v>
+        <v>37396800</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>1.38%→1.61%</t>
+          <t>1.43%→1.54%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
